--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98667</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129254331</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129254262</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129254588</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129254331</v>
+        <v>129254262</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579967</v>
+        <v>579939</v>
       </c>
       <c r="R2" t="n">
-        <v>7057143</v>
+        <v>7057140</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129254262</v>
+        <v>129254331</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579939</v>
+        <v>579967</v>
       </c>
       <c r="R3" t="n">
-        <v>7057140</v>
+        <v>7057143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129254588</v>
+        <v>129254437</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579970</v>
+        <v>579981</v>
       </c>
       <c r="R4" t="n">
-        <v>7057188</v>
+        <v>7057177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,6 +997,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129254588</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Taråbergen, Taråbergen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579970</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7057188</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45119-2022 artfynd.xlsx
+++ b/artfynd/A 45119-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254262</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254437</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,8 +1128,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254588</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>